--- a/backend/wp_templates/G/G8 其他权益工具投资.xlsx
+++ b/backend/wp_templates/G/G8 其他权益工具投资.xlsx
@@ -13411,7 +13411,7 @@
       <c r="K11" s="233"/>
       <c r="L11" s="233"/>
       <c r="M11" s="126">
-        <f>SUM(I11:L11)</f>
+        <f>SUM(I11:K11)</f>
         <v>0</v>
       </c>
       <c r="N11" s="233"/>
@@ -13420,7 +13420,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="126">
-        <f>D11+J11</f>
+        <f>D11+J11+K11</f>
         <v>0</v>
       </c>
       <c r="Q11" s="126">
@@ -13483,7 +13483,9 @@
         <v>0</v>
       </c>
       <c r="S12" s="233"/>
-      <c r="T12" s="126"/>
+      <c r="T12" s="126">
+        <f>Q12+S12</f>
+      </c>
       <c r="U12" s="239"/>
       <c r="V12" s="239"/>
       <c r="W12" s="238"/>
@@ -13517,14 +13519,16 @@
         <v>0</v>
       </c>
       <c r="P13" s="126">
-        <f t="shared" ref="P13:P20" si="6">D13+J13</f>
+        <f t="shared" ref="P13:P20" si="6">D13+J13+K13</f>
         <v>0</v>
       </c>
       <c r="Q13" s="126">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R13" s="233"/>
+      <c r="R13" s="233">
+        <f>F13+J13+L13</f>
+      </c>
       <c r="S13" s="233"/>
       <c r="T13" s="126">
         <f t="shared" ref="T13:T20" si="7">Q13+S13</f>
@@ -13570,7 +13574,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R14" s="233"/>
+      <c r="R14" s="233">
+        <f>F14+J14+L14</f>
+      </c>
       <c r="S14" s="233"/>
       <c r="T14" s="126">
         <f t="shared" si="7"/>
@@ -13616,7 +13622,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R15" s="233"/>
+      <c r="R15" s="233">
+        <f>F15+J15+L15</f>
+      </c>
       <c r="S15" s="233"/>
       <c r="T15" s="126">
         <f t="shared" si="7"/>
@@ -13662,7 +13670,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R16" s="233"/>
+      <c r="R16" s="233">
+        <f>F16+J16+L16</f>
+      </c>
       <c r="S16" s="233"/>
       <c r="T16" s="126">
         <f t="shared" si="7"/>
@@ -13708,7 +13718,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R17" s="233"/>
+      <c r="R17" s="233">
+        <f>F17+J17+L17</f>
+      </c>
       <c r="S17" s="233"/>
       <c r="T17" s="126">
         <f t="shared" si="7"/>
@@ -13754,7 +13766,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R18" s="233"/>
+      <c r="R18" s="233">
+        <f>F18+J18+L18</f>
+      </c>
       <c r="S18" s="233"/>
       <c r="T18" s="126">
         <f t="shared" si="7"/>
@@ -13800,7 +13814,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R19" s="233"/>
+      <c r="R19" s="233">
+        <f>F19+J19+L19</f>
+      </c>
       <c r="S19" s="233"/>
       <c r="T19" s="126">
         <f t="shared" si="7"/>
@@ -13846,7 +13862,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R20" s="233"/>
+      <c r="R20" s="233">
+        <f>F20+J20+L20</f>
+      </c>
       <c r="S20" s="233"/>
       <c r="T20" s="126">
         <f t="shared" si="7"/>
@@ -13893,8 +13911,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K21" s="142"/>
-      <c r="L21" s="142"/>
+      <c r="K21" s="142">
+        <f>SUM(K11:K20)</f>
+      </c>
+      <c r="L21" s="142">
+        <f>SUM(L11:L20)</f>
+      </c>
       <c r="M21" s="142">
         <f t="shared" ref="M21:N21" si="11">SUM(M11:M20)</f>
         <v>0</v>
@@ -13915,7 +13937,9 @@
         <f t="shared" ref="Q21:T21" si="13">SUM(Q11:Q20)</f>
         <v>0</v>
       </c>
-      <c r="R21" s="142"/>
+      <c r="R21" s="142">
+        <f>SUM(R11:R20)</f>
+      </c>
       <c r="S21" s="142">
         <f t="shared" si="13"/>
         <v>0</v>
